--- a/models/model_costs.xlsx
+++ b/models/model_costs.xlsx
@@ -1,36 +1,58 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30131"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\afbla\Documents\Imperial\final_project\models\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/4108010f6c0321c9/Documents/Imperial/final_project/models/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6287D5D8-F980-4F2C-B724-5C97AA658486}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="1" documentId="11_42C50FF9D219CFF4026F9BF73334E13F5659E76E" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{8B769FE6-C125-4A10-9D16-1E6EBC127D99}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="162913"/>
-  <extLst>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
-      <x15:workbookPr chartTrackingRefBase="1"/>
-    </ext>
-  </extLst>
+  <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="36" uniqueCount="22">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="208" uniqueCount="85">
   <si>
     <t>Model</t>
   </si>
   <si>
-    <t>Provider</t>
+    <t>Developed By</t>
+  </si>
+  <si>
+    <t>Geographic Origin</t>
+  </si>
+  <si>
+    <t>Platform</t>
+  </si>
+  <si>
+    <t>Size</t>
+  </si>
+  <si>
+    <t>Release Date</t>
+  </si>
+  <si>
+    <t>Model Type</t>
+  </si>
+  <si>
+    <t>Context Window</t>
+  </si>
+  <si>
+    <t>Parameters</t>
+  </si>
+  <si>
+    <t>Active Parameters</t>
+  </si>
+  <si>
+    <t>Quantization</t>
   </si>
   <si>
     <t>Input Tokens</t>
@@ -42,55 +64,217 @@
     <t>Output Tokens</t>
   </si>
   <si>
+    <t>Tool Calling Support</t>
+  </si>
+  <si>
     <t>Qwen3-VL-30B-A3B-Instruct</t>
   </si>
   <si>
+    <t>Alibaba</t>
+  </si>
+  <si>
+    <t>China</t>
+  </si>
+  <si>
     <t>DeepInfra</t>
   </si>
   <si>
+    <t>Small</t>
+  </si>
+  <si>
+    <t>MoE</t>
+  </si>
+  <si>
+    <t>256k</t>
+  </si>
+  <si>
+    <t>30B</t>
+  </si>
+  <si>
+    <t>3B</t>
+  </si>
+  <si>
+    <t>fp8</t>
+  </si>
+  <si>
+    <t>NA</t>
+  </si>
+  <si>
+    <t>Yes</t>
+  </si>
+  <si>
     <t>Qwen3-VL-235B-A22B-Instruct</t>
   </si>
   <si>
+    <t>Large</t>
+  </si>
+  <si>
+    <t>235B</t>
+  </si>
+  <si>
+    <t>22B</t>
+  </si>
+  <si>
     <t>ministral-3b</t>
   </si>
   <si>
+    <t>Mistral</t>
+  </si>
+  <si>
+    <t>France</t>
+  </si>
+  <si>
+    <t>Dense</t>
+  </si>
+  <si>
+    <t>-</t>
+  </si>
+  <si>
     <t>ministral-14b</t>
   </si>
   <si>
+    <t>14B</t>
+  </si>
+  <si>
     <t>deepseek-v4-flash</t>
   </si>
   <si>
+    <t>DeepSeek</t>
+  </si>
+  <si>
+    <t>2026-04-24*</t>
+  </si>
+  <si>
+    <t>1M</t>
+  </si>
+  <si>
+    <t>284B</t>
+  </si>
+  <si>
+    <t>13B</t>
+  </si>
+  <si>
     <t>deepseek-v4-pro</t>
   </si>
   <si>
-    <t>Mistral</t>
-  </si>
-  <si>
-    <t>DeepSeek</t>
-  </si>
-  <si>
-    <t>NVIDIA-Nemotron-3-Super-120B-A12B</t>
+    <t xml:space="preserve">1M </t>
+  </si>
+  <si>
+    <t>1.6T</t>
+  </si>
+  <si>
+    <t>49B</t>
+  </si>
+  <si>
+    <t>Nemotron-3-Nano-30B-A3B</t>
+  </si>
+  <si>
+    <t>NVIDIA</t>
+  </si>
+  <si>
+    <t>United States</t>
+  </si>
+  <si>
+    <t>fp4</t>
+  </si>
+  <si>
+    <t>Nemotron-3-Super-120B-A12B</t>
+  </si>
+  <si>
+    <t>120B</t>
+  </si>
+  <si>
+    <t>12B</t>
+  </si>
+  <si>
+    <t>bfloat</t>
   </si>
   <si>
     <t>GLM-4.7-Flash</t>
   </si>
   <si>
+    <t>Z.ai</t>
+  </si>
+  <si>
+    <t>198k</t>
+  </si>
+  <si>
+    <t>bloat16</t>
+  </si>
+  <si>
     <t>GLM-4.7</t>
   </si>
   <si>
-    <t>NA</t>
-  </si>
-  <si>
-    <t>Nemotron-3-Nano-30B-A3B</t>
+    <t>355B</t>
+  </si>
+  <si>
+    <t>32B</t>
   </si>
   <si>
     <t>gpt-oss-20b</t>
   </si>
   <si>
+    <t>OpenAI</t>
+  </si>
+  <si>
     <t>Fireworks AI</t>
   </si>
   <si>
+    <t>131k</t>
+  </si>
+  <si>
+    <t>21B</t>
+  </si>
+  <si>
+    <t>3.6B</t>
+  </si>
+  <si>
     <t>gpt-oss-120b</t>
+  </si>
+  <si>
+    <t>117B</t>
+  </si>
+  <si>
+    <t>5.1B</t>
+  </si>
+  <si>
+    <t>Llama-3.1-8B-Instruct-Turbo</t>
+  </si>
+  <si>
+    <t>Meta</t>
+  </si>
+  <si>
+    <t>8B</t>
+  </si>
+  <si>
+    <t>No</t>
+  </si>
+  <si>
+    <t>Llama-3.1-70B-Instruct-Turbo</t>
+  </si>
+  <si>
+    <t>70B</t>
+  </si>
+  <si>
+    <t>Gemma-3-4B-it</t>
+  </si>
+  <si>
+    <t>Google</t>
+  </si>
+  <si>
+    <t>128k</t>
+  </si>
+  <si>
+    <t>4B</t>
+  </si>
+  <si>
+    <t>bfloat16</t>
+  </si>
+  <si>
+    <t>Gemma-3-27B-it</t>
+  </si>
+  <si>
+    <t>27B</t>
   </si>
 </sst>
 </file>
@@ -126,8 +310,9 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -408,17 +593,27 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:E13"/>
+  <dimension ref="A1:O17"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="35.7109375" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="12" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="12.42578125" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.28515625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.140625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="13.42578125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="17" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="12" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="12" customWidth="1"/>
+    <col min="6" max="6" width="12.5703125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="12.5703125" customWidth="1"/>
+    <col min="8" max="8" width="16" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="16" customWidth="1"/>
+    <col min="10" max="10" width="17.42578125" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="17.42578125" customWidth="1"/>
+    <col min="12" max="12" width="12.42578125" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.28515625" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="14.140625" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="19" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -434,209 +629,787 @@
       <c r="E1" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" t="s">
+        <v>8</v>
+      </c>
+      <c r="J1" t="s">
+        <v>9</v>
+      </c>
+      <c r="K1" t="s">
+        <v>10</v>
+      </c>
+      <c r="L1" t="s">
+        <v>11</v>
+      </c>
+      <c r="M1" t="s">
+        <v>12</v>
+      </c>
+      <c r="N1" t="s">
+        <v>13</v>
+      </c>
+      <c r="O1" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="2" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="B2" t="s">
-        <v>6</v>
-      </c>
-      <c r="C2">
+        <v>16</v>
+      </c>
+      <c r="C2" t="s">
+        <v>17</v>
+      </c>
+      <c r="D2" t="s">
+        <v>18</v>
+      </c>
+      <c r="E2" t="s">
+        <v>19</v>
+      </c>
+      <c r="F2" s="1">
+        <v>45934</v>
+      </c>
+      <c r="G2" t="s">
+        <v>20</v>
+      </c>
+      <c r="H2" t="s">
+        <v>21</v>
+      </c>
+      <c r="I2" t="s">
+        <v>22</v>
+      </c>
+      <c r="J2" t="s">
+        <v>23</v>
+      </c>
+      <c r="K2" t="s">
+        <v>24</v>
+      </c>
+      <c r="L2">
         <v>0.15</v>
       </c>
-      <c r="D2" t="s">
+      <c r="M2" t="s">
+        <v>25</v>
+      </c>
+      <c r="N2">
+        <v>0.6</v>
+      </c>
+      <c r="O2" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="3" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>27</v>
+      </c>
+      <c r="B3" t="s">
+        <v>16</v>
+      </c>
+      <c r="C3" t="s">
         <v>17</v>
       </c>
-      <c r="E2">
+      <c r="D3" t="s">
+        <v>18</v>
+      </c>
+      <c r="E3" t="s">
+        <v>28</v>
+      </c>
+      <c r="F3" s="1">
+        <v>45934</v>
+      </c>
+      <c r="G3" t="s">
+        <v>20</v>
+      </c>
+      <c r="H3" t="s">
+        <v>21</v>
+      </c>
+      <c r="I3" t="s">
+        <v>29</v>
+      </c>
+      <c r="J3" t="s">
+        <v>30</v>
+      </c>
+      <c r="K3" t="s">
+        <v>24</v>
+      </c>
+      <c r="L3">
+        <v>0.2</v>
+      </c>
+      <c r="M3">
+        <v>0.11</v>
+      </c>
+      <c r="N3">
+        <v>0.88</v>
+      </c>
+      <c r="O3" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="4" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>31</v>
+      </c>
+      <c r="B4" t="s">
+        <v>32</v>
+      </c>
+      <c r="C4" t="s">
+        <v>33</v>
+      </c>
+      <c r="D4" t="s">
+        <v>32</v>
+      </c>
+      <c r="E4" t="s">
+        <v>19</v>
+      </c>
+      <c r="F4" s="1">
+        <v>45993</v>
+      </c>
+      <c r="G4" t="s">
+        <v>34</v>
+      </c>
+      <c r="H4" t="s">
+        <v>21</v>
+      </c>
+      <c r="I4" t="s">
+        <v>23</v>
+      </c>
+      <c r="J4" t="s">
+        <v>35</v>
+      </c>
+      <c r="K4" t="s">
+        <v>35</v>
+      </c>
+      <c r="L4">
+        <v>0.1</v>
+      </c>
+      <c r="M4">
+        <v>0.01</v>
+      </c>
+      <c r="N4">
+        <v>0.1</v>
+      </c>
+      <c r="O4" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="5" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>36</v>
+      </c>
+      <c r="B5" t="s">
+        <v>32</v>
+      </c>
+      <c r="C5" t="s">
+        <v>33</v>
+      </c>
+      <c r="D5" t="s">
+        <v>32</v>
+      </c>
+      <c r="E5" t="s">
+        <v>28</v>
+      </c>
+      <c r="F5" s="1">
+        <v>45993</v>
+      </c>
+      <c r="G5" t="s">
+        <v>34</v>
+      </c>
+      <c r="H5" t="s">
+        <v>21</v>
+      </c>
+      <c r="I5" t="s">
+        <v>37</v>
+      </c>
+      <c r="J5" t="s">
+        <v>35</v>
+      </c>
+      <c r="K5" t="s">
+        <v>35</v>
+      </c>
+      <c r="L5">
+        <v>0.2</v>
+      </c>
+      <c r="M5">
+        <v>0.02</v>
+      </c>
+      <c r="N5">
+        <v>0.2</v>
+      </c>
+      <c r="O5" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="6" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>38</v>
+      </c>
+      <c r="B6" t="s">
+        <v>39</v>
+      </c>
+      <c r="C6" t="s">
+        <v>17</v>
+      </c>
+      <c r="D6" t="s">
+        <v>39</v>
+      </c>
+      <c r="E6" t="s">
+        <v>19</v>
+      </c>
+      <c r="F6" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="G6" t="s">
+        <v>20</v>
+      </c>
+      <c r="H6" t="s">
+        <v>41</v>
+      </c>
+      <c r="I6" t="s">
+        <v>42</v>
+      </c>
+      <c r="J6" t="s">
+        <v>43</v>
+      </c>
+      <c r="K6" t="s">
+        <v>35</v>
+      </c>
+      <c r="L6">
+        <v>0.14000000000000001</v>
+      </c>
+      <c r="M6">
+        <v>2.8E-3</v>
+      </c>
+      <c r="N6">
+        <v>0.28000000000000003</v>
+      </c>
+      <c r="O6" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="7" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>44</v>
+      </c>
+      <c r="B7" t="s">
+        <v>39</v>
+      </c>
+      <c r="C7" t="s">
+        <v>17</v>
+      </c>
+      <c r="D7" t="s">
+        <v>39</v>
+      </c>
+      <c r="E7" t="s">
+        <v>28</v>
+      </c>
+      <c r="F7" s="1">
+        <v>46136</v>
+      </c>
+      <c r="G7" t="s">
+        <v>20</v>
+      </c>
+      <c r="H7" t="s">
+        <v>45</v>
+      </c>
+      <c r="I7" t="s">
+        <v>46</v>
+      </c>
+      <c r="J7" t="s">
+        <v>47</v>
+      </c>
+      <c r="K7" t="s">
+        <v>35</v>
+      </c>
+      <c r="L7">
+        <v>0.435</v>
+      </c>
+      <c r="M7">
+        <v>3.6250000000000002E-3</v>
+      </c>
+      <c r="N7">
+        <v>0.87</v>
+      </c>
+      <c r="O7" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="8" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>48</v>
+      </c>
+      <c r="B8" t="s">
+        <v>49</v>
+      </c>
+      <c r="C8" t="s">
+        <v>50</v>
+      </c>
+      <c r="D8" t="s">
+        <v>18</v>
+      </c>
+      <c r="E8" t="s">
+        <v>19</v>
+      </c>
+      <c r="F8" s="1">
+        <v>46006</v>
+      </c>
+      <c r="G8" t="s">
+        <v>20</v>
+      </c>
+      <c r="H8" t="s">
+        <v>21</v>
+      </c>
+      <c r="I8" t="s">
+        <v>22</v>
+      </c>
+      <c r="J8" t="s">
+        <v>23</v>
+      </c>
+      <c r="K8" t="s">
+        <v>51</v>
+      </c>
+      <c r="L8">
+        <v>0.05</v>
+      </c>
+      <c r="M8" t="s">
+        <v>25</v>
+      </c>
+      <c r="N8">
+        <v>0.2</v>
+      </c>
+      <c r="O8" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="9" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>52</v>
+      </c>
+      <c r="B9" t="s">
+        <v>49</v>
+      </c>
+      <c r="C9" t="s">
+        <v>50</v>
+      </c>
+      <c r="D9" t="s">
+        <v>18</v>
+      </c>
+      <c r="E9" t="s">
+        <v>28</v>
+      </c>
+      <c r="F9" s="1">
+        <v>46092</v>
+      </c>
+      <c r="G9" t="s">
+        <v>20</v>
+      </c>
+      <c r="H9" t="s">
+        <v>21</v>
+      </c>
+      <c r="I9" t="s">
+        <v>53</v>
+      </c>
+      <c r="J9" t="s">
+        <v>54</v>
+      </c>
+      <c r="K9" t="s">
+        <v>55</v>
+      </c>
+      <c r="L9">
+        <v>8.5000000000000006E-2</v>
+      </c>
+      <c r="M9" t="s">
+        <v>25</v>
+      </c>
+      <c r="N9">
+        <v>0.4</v>
+      </c>
+      <c r="O9" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="10" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
+        <v>56</v>
+      </c>
+      <c r="B10" t="s">
+        <v>57</v>
+      </c>
+      <c r="C10" t="s">
+        <v>17</v>
+      </c>
+      <c r="D10" t="s">
+        <v>18</v>
+      </c>
+      <c r="E10" t="s">
+        <v>19</v>
+      </c>
+      <c r="F10" s="1">
+        <v>46041</v>
+      </c>
+      <c r="G10" t="s">
+        <v>20</v>
+      </c>
+      <c r="H10" t="s">
+        <v>58</v>
+      </c>
+      <c r="I10" t="s">
+        <v>22</v>
+      </c>
+      <c r="J10" t="s">
+        <v>23</v>
+      </c>
+      <c r="K10" t="s">
+        <v>59</v>
+      </c>
+      <c r="L10">
+        <v>0.06</v>
+      </c>
+      <c r="M10">
+        <v>0.01</v>
+      </c>
+      <c r="N10">
+        <v>0.4</v>
+      </c>
+      <c r="O10" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="11" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
+        <v>60</v>
+      </c>
+      <c r="B11" t="s">
+        <v>57</v>
+      </c>
+      <c r="C11" t="s">
+        <v>17</v>
+      </c>
+      <c r="D11" t="s">
+        <v>18</v>
+      </c>
+      <c r="E11" t="s">
+        <v>28</v>
+      </c>
+      <c r="F11" s="1">
+        <v>46013</v>
+      </c>
+      <c r="G11" t="s">
+        <v>20</v>
+      </c>
+      <c r="H11" t="s">
+        <v>58</v>
+      </c>
+      <c r="I11" t="s">
+        <v>61</v>
+      </c>
+      <c r="J11" t="s">
+        <v>62</v>
+      </c>
+      <c r="K11" t="s">
+        <v>51</v>
+      </c>
+      <c r="L11">
+        <v>0.4</v>
+      </c>
+      <c r="M11">
+        <v>0.08</v>
+      </c>
+      <c r="N11">
+        <v>1.75</v>
+      </c>
+      <c r="O11" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="12" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
+        <v>63</v>
+      </c>
+      <c r="B12" t="s">
+        <v>64</v>
+      </c>
+      <c r="C12" t="s">
+        <v>50</v>
+      </c>
+      <c r="D12" t="s">
+        <v>65</v>
+      </c>
+      <c r="E12" t="s">
+        <v>19</v>
+      </c>
+      <c r="F12" s="1">
+        <v>45873</v>
+      </c>
+      <c r="G12" t="s">
+        <v>20</v>
+      </c>
+      <c r="H12" t="s">
+        <v>66</v>
+      </c>
+      <c r="I12" t="s">
+        <v>67</v>
+      </c>
+      <c r="J12" t="s">
+        <v>68</v>
+      </c>
+      <c r="K12" t="s">
+        <v>35</v>
+      </c>
+      <c r="L12">
+        <v>7.0000000000000007E-2</v>
+      </c>
+      <c r="M12" t="s">
+        <v>25</v>
+      </c>
+      <c r="N12">
+        <v>0.3</v>
+      </c>
+      <c r="O12" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="13" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A13" t="s">
+        <v>69</v>
+      </c>
+      <c r="B13" t="s">
+        <v>64</v>
+      </c>
+      <c r="C13" t="s">
+        <v>50</v>
+      </c>
+      <c r="D13" t="s">
+        <v>65</v>
+      </c>
+      <c r="E13" t="s">
+        <v>28</v>
+      </c>
+      <c r="F13" s="1">
+        <v>45873</v>
+      </c>
+      <c r="G13" t="s">
+        <v>20</v>
+      </c>
+      <c r="H13" t="s">
+        <v>66</v>
+      </c>
+      <c r="I13" t="s">
+        <v>70</v>
+      </c>
+      <c r="J13" t="s">
+        <v>71</v>
+      </c>
+      <c r="K13" t="s">
+        <v>35</v>
+      </c>
+      <c r="L13">
+        <v>0.15</v>
+      </c>
+      <c r="M13">
+        <v>1.4999999999999999E-2</v>
+      </c>
+      <c r="N13">
         <v>0.6</v>
       </c>
-    </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A3" t="s">
-        <v>7</v>
-      </c>
-      <c r="B3" t="s">
-        <v>6</v>
-      </c>
-      <c r="C3">
-        <v>0.2</v>
-      </c>
-      <c r="D3">
-        <v>0.11</v>
-      </c>
-      <c r="E3">
-        <v>0.88</v>
-      </c>
-    </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A4" t="s">
-        <v>8</v>
-      </c>
-      <c r="B4" t="s">
-        <v>12</v>
-      </c>
-      <c r="C4">
-        <v>0.1</v>
-      </c>
-      <c r="D4" t="s">
-        <v>17</v>
-      </c>
-      <c r="E4">
-        <v>0.1</v>
-      </c>
-    </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A5" t="s">
-        <v>9</v>
-      </c>
-      <c r="B5" t="s">
-        <v>12</v>
-      </c>
-      <c r="C5">
-        <v>0.2</v>
-      </c>
-      <c r="D5" t="s">
-        <v>17</v>
-      </c>
-      <c r="E5">
-        <v>0.2</v>
-      </c>
-    </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A6" t="s">
-        <v>10</v>
-      </c>
-      <c r="B6" t="s">
-        <v>13</v>
-      </c>
-      <c r="C6">
-        <v>0.14000000000000001</v>
-      </c>
-      <c r="D6">
-        <v>2.8E-3</v>
-      </c>
-      <c r="E6">
-        <v>0.28000000000000003</v>
-      </c>
-    </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A7" t="s">
-        <v>11</v>
-      </c>
-      <c r="B7" t="s">
-        <v>6</v>
-      </c>
-      <c r="C7">
-        <v>0.435</v>
-      </c>
-      <c r="D7">
-        <v>3.6250000000000002E-3</v>
-      </c>
-      <c r="E7">
-        <v>0.87</v>
-      </c>
-    </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A8" t="s">
+      <c r="O13" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="14" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A14" t="s">
+        <v>72</v>
+      </c>
+      <c r="B14" t="s">
+        <v>73</v>
+      </c>
+      <c r="C14" t="s">
+        <v>50</v>
+      </c>
+      <c r="D14" t="s">
         <v>18</v>
       </c>
-      <c r="B8" t="s">
-        <v>6</v>
-      </c>
-      <c r="C8">
-        <v>0.05</v>
-      </c>
-      <c r="D8" t="s">
-        <v>17</v>
-      </c>
-      <c r="E8">
-        <v>0.2</v>
-      </c>
-    </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A9" t="s">
-        <v>14</v>
-      </c>
-      <c r="B9" t="s">
-        <v>6</v>
-      </c>
-      <c r="C9">
-        <v>8.5000000000000006E-2</v>
-      </c>
-      <c r="D9" t="s">
-        <v>17</v>
-      </c>
-      <c r="E9">
-        <v>0.4</v>
-      </c>
-    </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A10" t="s">
-        <v>15</v>
-      </c>
-      <c r="B10" t="s">
-        <v>6</v>
-      </c>
-      <c r="C10">
-        <v>0.06</v>
-      </c>
-      <c r="D10">
-        <v>0.01</v>
-      </c>
-      <c r="E10">
-        <v>0.4</v>
-      </c>
-    </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A11" t="s">
-        <v>16</v>
-      </c>
-      <c r="B11" t="s">
-        <v>6</v>
-      </c>
-      <c r="C11">
-        <v>0.4</v>
-      </c>
-      <c r="D11">
-        <v>0.08</v>
-      </c>
-      <c r="E11">
-        <v>1.75</v>
-      </c>
-    </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A12" t="s">
+      <c r="E14" t="s">
         <v>19</v>
       </c>
-      <c r="B12" t="s">
-        <v>20</v>
-      </c>
-      <c r="C12">
-        <v>7.0000000000000007E-2</v>
-      </c>
-      <c r="D12" t="s">
-        <v>17</v>
-      </c>
-      <c r="E12">
-        <v>0.3</v>
-      </c>
-    </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A13" t="s">
-        <v>21</v>
-      </c>
-      <c r="B13" t="s">
-        <v>20</v>
-      </c>
-      <c r="C13">
-        <v>0.15</v>
-      </c>
-      <c r="D13" t="s">
-        <v>17</v>
-      </c>
-      <c r="E13">
-        <v>0.6</v>
+      <c r="F14" s="1">
+        <v>45496</v>
+      </c>
+      <c r="G14" t="s">
+        <v>34</v>
+      </c>
+      <c r="H14" t="s">
+        <v>66</v>
+      </c>
+      <c r="I14" t="s">
+        <v>74</v>
+      </c>
+      <c r="J14" t="s">
+        <v>35</v>
+      </c>
+      <c r="K14" t="s">
+        <v>35</v>
+      </c>
+      <c r="L14" t="s">
+        <v>25</v>
+      </c>
+      <c r="M14" t="s">
+        <v>25</v>
+      </c>
+      <c r="N14" t="s">
+        <v>25</v>
+      </c>
+      <c r="O14" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="15" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A15" t="s">
+        <v>76</v>
+      </c>
+      <c r="B15" t="s">
+        <v>73</v>
+      </c>
+      <c r="C15" t="s">
+        <v>50</v>
+      </c>
+      <c r="D15" t="s">
+        <v>18</v>
+      </c>
+      <c r="E15" t="s">
+        <v>28</v>
+      </c>
+      <c r="F15" s="1">
+        <v>45496</v>
+      </c>
+      <c r="G15" t="s">
+        <v>34</v>
+      </c>
+      <c r="H15" t="s">
+        <v>66</v>
+      </c>
+      <c r="I15" t="s">
+        <v>77</v>
+      </c>
+      <c r="J15" t="s">
+        <v>35</v>
+      </c>
+      <c r="K15" t="s">
+        <v>35</v>
+      </c>
+      <c r="L15" t="s">
+        <v>25</v>
+      </c>
+      <c r="M15" t="s">
+        <v>25</v>
+      </c>
+      <c r="N15" t="s">
+        <v>25</v>
+      </c>
+      <c r="O15" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="16" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A16" t="s">
+        <v>78</v>
+      </c>
+      <c r="B16" t="s">
+        <v>79</v>
+      </c>
+      <c r="C16" t="s">
+        <v>50</v>
+      </c>
+      <c r="D16" t="s">
+        <v>18</v>
+      </c>
+      <c r="E16" t="s">
+        <v>19</v>
+      </c>
+      <c r="F16" s="1">
+        <v>45726</v>
+      </c>
+      <c r="G16" t="s">
+        <v>34</v>
+      </c>
+      <c r="H16" t="s">
+        <v>80</v>
+      </c>
+      <c r="I16" t="s">
+        <v>81</v>
+      </c>
+      <c r="J16" t="s">
+        <v>81</v>
+      </c>
+      <c r="K16" t="s">
+        <v>82</v>
+      </c>
+      <c r="L16" t="s">
+        <v>25</v>
+      </c>
+      <c r="M16" t="s">
+        <v>25</v>
+      </c>
+      <c r="N16" t="s">
+        <v>25</v>
+      </c>
+      <c r="O16" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="17" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A17" t="s">
+        <v>83</v>
+      </c>
+      <c r="B17" t="s">
+        <v>79</v>
+      </c>
+      <c r="C17" t="s">
+        <v>50</v>
+      </c>
+      <c r="D17" t="s">
+        <v>18</v>
+      </c>
+      <c r="E17" t="s">
+        <v>28</v>
+      </c>
+      <c r="F17" s="1">
+        <v>45726</v>
+      </c>
+      <c r="G17" t="s">
+        <v>34</v>
+      </c>
+      <c r="H17" t="s">
+        <v>80</v>
+      </c>
+      <c r="I17" t="s">
+        <v>84</v>
+      </c>
+      <c r="J17" t="s">
+        <v>84</v>
+      </c>
+      <c r="K17" t="s">
+        <v>24</v>
+      </c>
+      <c r="L17" t="s">
+        <v>25</v>
+      </c>
+      <c r="M17" t="s">
+        <v>25</v>
+      </c>
+      <c r="N17" t="s">
+        <v>25</v>
+      </c>
+      <c r="O17" t="s">
+        <v>75</v>
       </c>
     </row>
   </sheetData>
